--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-authorization-date.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-date</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization-date</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
